--- a/web/public/templates/usa_expense_report_template.xlsx
+++ b/web/public/templates/usa_expense_report_template.xlsx
@@ -954,37 +954,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Unknown User</author>
-  </authors>
-  <commentList>
-    <comment ref="F5" authorId="0" shapeId="0">
-      <text>
-        <t>可以选择报销币种
-  - 吴燕飞sherry</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>wljqr</author>
-  </authors>
-  <commentList>
-    <comment ref="C3" authorId="0" shapeId="0">
-      <text>
-        <t>可以选择报销币种</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -2347,7 +2316,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" scale="36"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -3409,6 +3377,5 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>